--- a/test/003_UT-画面遷移テスト/画面遷移テスト仕様書.xlsx
+++ b/test/003_UT-画面遷移テスト/画面遷移テスト仕様書.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>テストID：UT-FLOW-001 ～ UT-FLOW-018　　テスト確認観点：画面遷移・データ整合性全条件網羅テスト</t>
+          <t>テストID：UT-FLOW-001 ～ UT-FLOW-027　　テスト確認観点：画面遷移・データ整合性全条件網羅テスト</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
     </row>
-    <row r="23">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>UT-FLOW-016</t>
@@ -1011,7 +1011,7 @@
       <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="8" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="24" ht="38" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
           <t>UT-FLOW-017</t>
@@ -1036,7 +1036,7 @@
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="25" ht="38" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>UT-FLOW-018</t>
@@ -1061,14 +1061,247 @@
       <c r="F25" s="8" t="inlineStr"/>
       <c r="G25" s="8" t="inlineStr"/>
     </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>■ 画面詳細表示・ソート機能確認（019〜027）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="38" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>UT-FLOW-019</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>login.html</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>ブラウザで login.html を開き、ページ全体の UI を目視確認する</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>会社ロゴ・代理店コード・ログインID・パスワード入力欄・ログインボタン・パスワードお忘れリンクが表示されること</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>UT-FLOW-020</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>dashboard.html</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>A001/admin でログインしてダッシュボードの更改状況グラフを目視確認する</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>今月更改グラフ中央に「28件完了」・完了率バッジ「11.3%」、翌月更改グラフ中央に「125件完了」・完了率バッジ「38.5%」が表示されること</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr"/>
+      <c r="G28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>UT-FLOW-021</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>maturity.html</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>A001でログインして満期管理画面を表示し、一覧カラムと件数を目視確認する</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>満期年月日・証券番号・顧客名・種目・担当者・連絡手段/連絡先・年換算保険料・事故・異動・メモ・発送予定日・帳票・FC-STS・更改STS の各カラムが表示され、検索結果：5件と表示されること</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="38" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>UT-FLOW-022</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>maturity.html</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>満期管理一覧で任意の行の「＋」ボタンをクリックしてアコーディオン詳細を展開する</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>展開行に「更改後証券番号」「更改後年換算保険料」「アップセルSTS」「落ちSTS」「メモ」の詳細情報が表示されること</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr"/>
+      <c r="G30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31" ht="38" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>UT-FLOW-023</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>maturity.html</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>フォローコールSTS プルダウンで「未実施」を選択して検索ボタンをクリックする</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>検索結果が絞り込まれ「検索結果：2件」と表示されること（山田 直子・中村 浩司）</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>UT-FLOW-024</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>maturity.html</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>フォローコールSTS「未実施」絞込の状態で「担当者」列ヘッダーをクリックして昇順ソートする</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>担当者列ヘッダーに昇順矢印（↑）が表示され、S001→S002の順に並び替わること</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr"/>
+      <c r="F32" s="8" t="inlineStr"/>
+      <c r="G32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>UT-FLOW-025</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>maturity.html</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>検索条件をクリアした後「満期年月日」列ヘッダーをクリックして昇順ソートする</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>満期年月日列ヘッダーに昇順矢印（↑）が表示され、2026-03-20 → 2026-04-15 → 2026-05-10 → 2026-05-31 → 2026-06-15 の順に並び替わること</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>UT-FLOW-026</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>maturity.html</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>「担当者」列ヘッダーをクリックして昇順ソートする（全件表示）</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>担当者列ヘッダーに昇順矢印（↑）が表示され、S001（3件）→ S002（2件）の順に並び替わること</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr"/>
+      <c r="G34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>UT-FLOW-027</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>maturity.html</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>「年換算保険料」列ヘッダーをクリックして昇順ソートする（全件表示）</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>年換算保険料列ヘッダーに昇順矢印（↑）が表示され、¥45,000 → ¥85,000 → ¥95,000 → ¥120,000 → ¥150,000 の順に並び替わること</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
